--- a/Tools/Luban/DataTables/Datas/UIWindow.xlsx
+++ b/Tools/Luban/DataTables/Datas/UIWindow.xlsx
@@ -17,75 +17,39 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>july</author>
+    <author>xiaojia</author>
   </authors>
   <commentList>
     <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>july:</t>
+          <t>july:
+0 : 无动画
+1 : Aniamtor
+3 : 缩放</t>
         </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="1">
+      <text>
         <r>
           <rPr>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">
-0 : 无动画
-1 : 缩放动画
-2 : 自定义动画</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>july:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0:永不销毁
-1:关闭一段时间后销毁
-2:关闭后即可销毁</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>july:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-单位为s</t>
+          <t>xiaojia:
+Background = 0,      // 背景层（如场景背景）
+Normal = 100,        // 普通层（主界面、功能界面）
+Popup = 200,         // 弹窗层（对话框、提示框）
+Top = 300,           // 顶层（系统提示、公告）
+Loading = 400,       // 加载层（加载界面）
+Guide = 500          // 引导层（新手引导、遮罩）</t>
         </r>
       </text>
     </comment>
@@ -94,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -120,10 +84,10 @@
     <t>exitAnimType</t>
   </si>
   <si>
-    <t>liftState</t>
-  </si>
-  <si>
-    <t>destroyTime</t>
+    <t>isIgnoreSafeArea</t>
+  </si>
+  <si>
+    <t>uiLayer</t>
   </si>
   <si>
     <t>##type</t>
@@ -162,46 +126,16 @@
     <t>关闭窗口的动画类型</t>
   </si>
   <si>
-    <t>销毁条件</t>
-  </si>
-  <si>
-    <t>隐藏多少时间后销毁</t>
-  </si>
-  <si>
-    <t>存档选择界面</t>
-  </si>
-  <si>
-    <t>UISelectArchiveWindow</t>
-  </si>
-  <si>
-    <t>创建新存档界面</t>
-  </si>
-  <si>
-    <t>UINewGameWindow</t>
-  </si>
-  <si>
-    <t>主界面窗口</t>
-  </si>
-  <si>
-    <t>UIMainHud</t>
-  </si>
-  <si>
-    <t>副本HUD</t>
-  </si>
-  <si>
-    <t>UIDungeonSelectWindow</t>
-  </si>
-  <si>
-    <t>战斗HUD</t>
-  </si>
-  <si>
-    <t>UIBattleHud</t>
-  </si>
-  <si>
-    <t>战斗胜利界面</t>
-  </si>
-  <si>
-    <t>UIBattleVictoryWindow</t>
+    <t>是否忽略安全区域</t>
+  </si>
+  <si>
+    <t>层级</t>
+  </si>
+  <si>
+    <t>通用领奖界面</t>
+  </si>
+  <si>
+    <t>UIAwardDisplayWindow</t>
   </si>
 </sst>
 </file>
@@ -214,7 +148,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,13 +301,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -683,159 +611,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1157,29 +1082,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.14285714285714" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.2857142857143" style="1" customWidth="1"/>
-    <col min="5" max="8" width="20.7142857142857" customWidth="1"/>
-    <col min="9" max="9" width="11.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="21.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="8" width="20.7142857142857" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1194,7 +1119,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1202,16 +1127,16 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1226,24 +1151,24 @@
       <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1258,191 +1183,40 @@
       <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2">
-        <v>101</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    <row r="4" spans="2:10">
+      <c r="B4" s="1">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
       <c r="J4" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
-        <v>102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
-        <v>1001</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>2001</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>3001</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>4001</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="1">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
